--- a/artfynd/A 32813-2022 artfynd.xlsx
+++ b/artfynd/A 32813-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688682</v>
       </c>
       <c r="B2" t="n">
-        <v>91602</v>
+        <v>91607</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32813-2022 artfynd.xlsx
+++ b/artfynd/A 32813-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688682</v>
       </c>
       <c r="B2" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32813-2022 artfynd.xlsx
+++ b/artfynd/A 32813-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688682</v>
       </c>
       <c r="B2" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32813-2022 artfynd.xlsx
+++ b/artfynd/A 32813-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688682</v>
       </c>
       <c r="B2" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32813-2022 artfynd.xlsx
+++ b/artfynd/A 32813-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688682</v>
       </c>
       <c r="B2" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32813-2022 artfynd.xlsx
+++ b/artfynd/A 32813-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688682</v>
       </c>
       <c r="B2" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32813-2022 artfynd.xlsx
+++ b/artfynd/A 32813-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688682</v>
       </c>
       <c r="B2" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32813-2022 artfynd.xlsx
+++ b/artfynd/A 32813-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688682</v>
       </c>
       <c r="B2" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32813-2022 artfynd.xlsx
+++ b/artfynd/A 32813-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688682</v>
       </c>
       <c r="B2" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32813-2022 artfynd.xlsx
+++ b/artfynd/A 32813-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065342</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065324</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065343</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1151,6 +1171,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065260</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1278,8 +1303,20 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065261</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 32813-2022 artfynd.xlsx
+++ b/artfynd/A 32813-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135065342</v>
       </c>
       <c r="B2" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135065324</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>135065343</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>135065260</v>
       </c>
       <c r="B5" t="n">
-        <v>57153</v>
+        <v>57158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>135065261</v>
       </c>
       <c r="B6" t="n">
-        <v>57153</v>
+        <v>57158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32813-2022 artfynd.xlsx
+++ b/artfynd/A 32813-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135065342</v>
       </c>
       <c r="B2" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
